--- a/data/trans_bre/P19C09-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P19C09-Edad-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 1,96</t>
+          <t>-1,05; 1,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 3,41</t>
+          <t>-1,34; 3,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 1,07</t>
+          <t>-3,71; 1,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-74,74; 699,04</t>
+          <t>-76,96; 604,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-47,22; 308,95</t>
+          <t>-49,95; 330,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-75,41; 77,09</t>
+          <t>-76,49; 76,16</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,43</t>
+          <t>-1,53; 2,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 3,59</t>
+          <t>-0,14; 3,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 2,44</t>
+          <t>-2,1; 2,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-52,78; 248,24</t>
+          <t>-55,07; 190,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,13; 366,61</t>
+          <t>-13,61; 386,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-50,02; 125,76</t>
+          <t>-51,69; 120,79</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 1,13</t>
+          <t>-2,57; 0,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 3,19</t>
+          <t>-0,27; 3,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 0,59</t>
+          <t>-3,44; 0,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-68,77; 87,53</t>
+          <t>-67,62; 81,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-34,72; 547,43</t>
+          <t>-36,24; 500,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-72,42; 31,42</t>
+          <t>-73,54; 33,49</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 4,01</t>
+          <t>-0,54; 4,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 2,4</t>
+          <t>-0,77; 2,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,27</t>
+          <t>-1,4; 2,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,98; 599,3</t>
+          <t>-35,55; 600,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,75; 491,29</t>
+          <t>-49,57; 451,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,75; 190,74</t>
+          <t>-50,63; 205,95</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 5,87</t>
+          <t>-0,98; 5,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 2,71</t>
+          <t>-1,25; 2,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 4,67</t>
+          <t>-0,23; 4,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-23,76; 287,8</t>
+          <t>-21,28; 331,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-72,04; 339,12</t>
+          <t>-53,45; 348,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-36,46; 515,95</t>
+          <t>-24,86; 585,03</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 5,51</t>
+          <t>-2,58; 5,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 1,11</t>
+          <t>-5,24; 1,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 2,3</t>
+          <t>-2,37; 2,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-36,53; 199,34</t>
+          <t>-41,86; 194,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-81,65; 96,91</t>
+          <t>-83,56; 91,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-76,93; 296,54</t>
+          <t>-79,94; 337,9</t>
         </is>
       </c>
     </row>
@@ -1114,22 +1114,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 1,26</t>
+          <t>-10,83; 1,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 7,52</t>
+          <t>1,58; 7,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 0,99</t>
+          <t>-7,73; 1,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-78,16; 42,49</t>
+          <t>-79,3; 35,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-91,32; 66,19</t>
+          <t>-89,95; 76,98</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,46</t>
+          <t>-0,34; 1,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,95</t>
+          <t>0,31; 1,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,66</t>
+          <t>-1,1; 0,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 68,66</t>
+          <t>-11,74; 69,72</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,85; 142,09</t>
+          <t>13,82; 140,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-32,83; 27,7</t>
+          <t>-33,27; 29,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C09-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P19C09-Edad-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 1,81</t>
+          <t>-1,21; 1,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 3,54</t>
+          <t>-1,3; 3,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 1,23</t>
+          <t>-3,85; 1,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-76,96; 604,08</t>
+          <t>-78,39; 591,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-49,95; 330,36</t>
+          <t>-45,27; 288,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-76,49; 76,16</t>
+          <t>-76,93; 78,2</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 2,22</t>
+          <t>-1,33; 2,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,84</t>
+          <t>-0,05; 3,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 2,47</t>
+          <t>-1,98; 2,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-55,07; 190,89</t>
+          <t>-54,21; 217,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 386,66</t>
+          <t>-9,32; 320,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-51,69; 120,79</t>
+          <t>-49,42; 135,88</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 0,9</t>
+          <t>-2,69; 0,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 3,26</t>
+          <t>-0,34; 3,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 0,65</t>
+          <t>-3,42; 0,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-67,62; 81,15</t>
+          <t>-73,64; 64,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-36,24; 500,46</t>
+          <t>-40,01; 549,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-73,54; 33,49</t>
+          <t>-72,57; 37,12</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 4,1</t>
+          <t>-0,49; 4,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 2,46</t>
+          <t>-0,8; 2,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 2,41</t>
+          <t>-1,46; 2,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-35,55; 600,87</t>
+          <t>-32,3; 633,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,57; 451,01</t>
+          <t>-54,56; 473,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,63; 205,95</t>
+          <t>-50,26; 196,4</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 5,77</t>
+          <t>-0,98; 5,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 2,99</t>
+          <t>-1,51; 2,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 4,47</t>
+          <t>-0,38; 4,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,28; 331,34</t>
+          <t>-21,01; 291,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-53,45; 348,7</t>
+          <t>-64,78; 389,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-24,86; 585,03</t>
+          <t>-24,55; 564,53</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 5,17</t>
+          <t>-2,34; 5,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 1,31</t>
+          <t>-5,63; 1,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 2,51</t>
+          <t>-2,31; 2,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-41,86; 194,65</t>
+          <t>-40,13; 210,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-83,56; 91,82</t>
+          <t>-81,64; 99,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-79,94; 337,9</t>
+          <t>-75,16; 313,31</t>
         </is>
       </c>
     </row>
@@ -1114,22 +1114,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 1,27</t>
+          <t>-11,36; 0,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 7,36</t>
+          <t>1,87; 7,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 1,14</t>
+          <t>-7,98; 0,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-79,3; 35,98</t>
+          <t>-80,43; 23,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-89,95; 76,98</t>
+          <t>-90,86; 81,69</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,45</t>
+          <t>-0,35; 1,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,93</t>
+          <t>0,27; 1,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,7</t>
+          <t>-1,05; 0,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 69,72</t>
+          <t>-11,64; 66,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,82; 140,94</t>
+          <t>12,43; 136,76</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-33,27; 29,64</t>
+          <t>-32,54; 30,67</t>
         </is>
       </c>
     </row>
